--- a/turnuva_verileri.xlsx
+++ b/turnuva_verileri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kübra GÜZEL\OneDrive\Masaüstü\Turnuva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A111EA13-06BB-4AB9-9966-645E4ABD7475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1359080D-201E-41C3-BC71-5A6A1E4FFB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2615,8 +2615,12 @@
       <c r="G36" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="7"/>
+      <c r="H36" s="4">
+        <v>2</v>
+      </c>
+      <c r="I36" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="37" spans="1:9" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
